--- a/government-data-extractor/output/government_schemes.xlsx
+++ b/government-data-extractor/output/government_schemes.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B635D7-CE89-4292-AD6A-E265D9C31F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Schemes" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Schemes" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="306">
   <si>
     <t>S.No</t>
   </si>
   <si>
+    <t>UI/UX Program Type</t>
+  </si>
+  <si>
+    <t>Scheme Name (official)</t>
+  </si>
+  <si>
     <t>UI/UX Short Description</t>
   </si>
   <si>
@@ -29,15 +31,9 @@
     <t>UI/UX Reference Link</t>
   </si>
   <si>
-    <t>UI/UX Program Type</t>
-  </si>
-  <si>
     <t>Scheme ID</t>
   </si>
   <si>
-    <t>Scheme Name (official)</t>
-  </si>
-  <si>
     <t>Acronym</t>
   </si>
   <si>
@@ -200,6 +196,12 @@
     <t>Catchy Line/Hook</t>
   </si>
   <si>
+    <t>Grant</t>
+  </si>
+  <si>
+    <t>First Home Owner (New Homes) Grant</t>
+  </si>
+  <si>
     <t>Eligible first home buyers can receive a $10,000 grant when purchasing or building a home in NSW.</t>
   </si>
   <si>
@@ -209,15 +211,9 @@
     <t>https://www.revenue.nsw.gov.au/grants-schemes/first-home-owner-new-homes-grant</t>
   </si>
   <si>
-    <t>Grant</t>
-  </si>
-  <si>
     <t>nsw-first-home-owner-grant</t>
   </si>
   <si>
-    <t>First Home Owner (New Homes) Grant</t>
-  </si>
-  <si>
     <t>FHOG</t>
   </si>
   <si>
@@ -296,7 +292,7 @@
     <t>Via conveyancer/solicitor at settlement</t>
   </si>
   <si>
-    <t>2026-07-09</t>
+    <t>2026-07-17</t>
   </si>
   <si>
     <t>www.revenue.nsw.gov.au</t>
@@ -311,6 +307,9 @@
     <t>Get $10,000 towards your first home.</t>
   </si>
   <si>
+    <t>First Home Owner Grant</t>
+  </si>
+  <si>
     <t>Eligible first home buyers can receive a $10,000 grant when purchasing or building a new home in VIC.</t>
   </si>
   <si>
@@ -323,9 +322,6 @@
     <t>vic-first-home-owner-grant</t>
   </si>
   <si>
-    <t>First Home Owner Grant</t>
-  </si>
-  <si>
     <t>State Revenue Office Victoria</t>
   </si>
   <si>
@@ -350,6 +346,9 @@
     <t>www.sro.vic.gov.au</t>
   </si>
   <si>
+    <t>First home owner grant</t>
+  </si>
+  <si>
     <t>Eligible first home buyers can receive a $30,000 grant when purchasing or building a new home in QLD.</t>
   </si>
   <si>
@@ -362,9 +361,6 @@
     <t>qld-first-home-owner-grant</t>
   </si>
   <si>
-    <t>First home owner grant</t>
-  </si>
-  <si>
     <t>Queensland Revenue Office</t>
   </si>
   <si>
@@ -488,6 +484,9 @@
     <t>A cash boost for your first home.</t>
   </si>
   <si>
+    <t>HomeGrown Territory Grant</t>
+  </si>
+  <si>
     <t>Eligible first home buyers can receive a $10,000 grant when purchasing or building a home in NT.</t>
   </si>
   <si>
@@ -500,9 +499,6 @@
     <t>nt-homegrown-territory-grant</t>
   </si>
   <si>
-    <t>HomeGrown Territory Grant</t>
-  </si>
-  <si>
     <t>HTG</t>
   </si>
   <si>
@@ -533,25 +529,25 @@
     <t>treasury.nt.gov.au</t>
   </si>
   <si>
+    <t>Scheme</t>
+  </si>
+  <si>
+    <t>Australian Government 5% Deposit Scheme</t>
+  </si>
+  <si>
     <t>Eligible first home buyers can purchase a home with as little as a 5% deposit without paying Lenders Mortgage Insurance.</t>
   </si>
   <si>
-    <t>The First Home Guarantee allows eligible first home buyers to purchase a home with a minimum 5% deposit. The Australian Government guarantees part of the loan, helping eligible borrowers avoid paying Lenders Mortgage Insurance.</t>
-  </si>
-  <si>
-    <t>https://www.housingaustralia.gov.au/home-guarantee-scheme</t>
-  </si>
-  <si>
-    <t>Scheme</t>
-  </si>
-  <si>
-    <t>fed-first-home-guarantee</t>
-  </si>
-  <si>
-    <t>First Home Guarantee</t>
-  </si>
-  <si>
-    <t>FHBG</t>
+    <t>The Australian Government 5% Deposit Scheme allows eligible first home buyers to purchase a home with a minimum 5% deposit. The Australian Government guarantees part of the loan, helping eligible borrowers avoid paying Lenders Mortgage Insurance.</t>
+  </si>
+  <si>
+    <t>https://firsthomebuyers.gov.au/australian-government-5-percent-deposit-scheme</t>
+  </si>
+  <si>
+    <t>fed-5-percent-deposit-scheme</t>
+  </si>
+  <si>
+    <t>AGDS</t>
   </si>
   <si>
     <t>Guarantee</t>
@@ -566,6 +562,12 @@
     <t>All States &amp; Territories</t>
   </si>
   <si>
+    <t>Metro and regional (different caps may apply)</t>
+  </si>
+  <si>
+    <t>Use the Postcode Search Tool on the First Home Buyers website to check the price cap for the location you want to buy in.</t>
+  </si>
+  <si>
     <t>Government guarantee (avoids LMI)</t>
   </si>
   <si>
@@ -575,73 +577,64 @@
     <t>Buy with 5% deposit, government guarantees the balance to avoid LMI</t>
   </si>
   <si>
-    <t>New home; Apartment/Unit; Townhouse</t>
+    <t>$1,500,000</t>
+  </si>
+  <si>
+    <t>Varies by location: $1,500,000, $800,000, $950,000</t>
+  </si>
+  <si>
+    <t>Must not have owned property in Australia in the last 10 years</t>
   </si>
   <si>
     <t>Single parent</t>
   </si>
   <si>
-    <t>www.housingaustralia.gov.au</t>
-  </si>
-  <si>
-    <t>Please note that not all benefits, features, or entitlements listed may be applicable across all Schemes.</t>
+    <t>1 October 2025</t>
+  </si>
+  <si>
+    <t>1 July 2026</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>Statutory Declarations Act 1959; National Consumer Credit Protection Act 2009; Australian Citizenship Act 2007</t>
+  </si>
+  <si>
+    <t>firsthomebuyers.gov.au</t>
+  </si>
+  <si>
+    <t>Making a false or misleading statement is a serious offence •important: Part D is a Commonwealth Statutory Declaration.</t>
   </si>
   <si>
     <t>Low deposit, no LMI</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Buy with a low deposit — no Lenders Mortgage Insurance.</t>
   </si>
   <si>
-    <t>The Family Home Guarantee allows eligible first home buyers to purchase a home with a minimum 5% deposit. The Australian Government guarantees part of the loan, helping eligible borrowers avoid paying Lenders Mortgage Insurance.</t>
-  </si>
-  <si>
-    <t>fed-family-home-guarantee</t>
-  </si>
-  <si>
-    <t>Family Home Guarantee</t>
-  </si>
-  <si>
-    <t>FHG</t>
-  </si>
-  <si>
-    <t>The Regional First Home Buyer Guarantee allows eligible first home buyers to purchase a home with a minimum 5% deposit. The Australian Government guarantees part of the loan, helping eligible borrowers avoid paying Lenders Mortgage Insurance.</t>
-  </si>
-  <si>
-    <t>fed-regional-first-home-buyer-guarantee</t>
-  </si>
-  <si>
-    <t>Regional First Home Buyer Guarantee</t>
-  </si>
-  <si>
-    <t>RFHBG</t>
+    <t>Australian Government Help to Buy Scheme</t>
   </si>
   <si>
     <t>The government contributes toward the purchase price so eligible first home buyers can buy their first home with a smaller deposit.</t>
   </si>
   <si>
-    <t>Under the Help to Buy, the Australian Government contributes toward the purchase price of a home, reducing the deposit and loan an eligible first home buyer needs. Eligibility requirements are defined by Housing Australia.</t>
-  </si>
-  <si>
-    <t>https://www.housingaustralia.gov.au/home-guarantee-scheme/help-buy</t>
+    <t>Under the Australian Government Help to Buy Scheme, the Australian Government contributes toward the purchase price of a home, reducing the deposit and loan an eligible first home buyer needs. Applicants must satisfy residency, occupancy and income requirements defined by Housing Australia.</t>
+  </si>
+  <si>
+    <t>https://firsthomebuyers.gov.au/australian-government-help-buy-scheme</t>
   </si>
   <si>
     <t>fed-help-to-buy</t>
   </si>
   <si>
-    <t>Help to Buy</t>
-  </si>
-  <si>
     <t>HTB</t>
   </si>
   <si>
     <t>Shared Equity</t>
   </si>
   <si>
-    <t>Up to 5% equity contribution</t>
+    <t>Up to 2% equity contribution</t>
   </si>
   <si>
     <t>Equity share</t>
@@ -650,27 +643,51 @@
     <t>Government co-purchases a share of the property</t>
   </si>
   <si>
+    <t>Australian citizen</t>
+  </si>
+  <si>
+    <t>$103,000</t>
+  </si>
+  <si>
+    <t>$165,000</t>
+  </si>
+  <si>
+    <t>Taxable income</t>
+  </si>
+  <si>
+    <t>New home; Established home; Apartment/Unit; Townhouse</t>
+  </si>
+  <si>
+    <t>2%</t>
+  </si>
+  <si>
+    <t>You cannot apply directly to Housing Australia for Help to Buy.</t>
+  </si>
+  <si>
+    <t>10,000 places</t>
+  </si>
+  <si>
     <t>Shared equity</t>
   </si>
   <si>
     <t>Let the government co-buy your first home.</t>
   </si>
   <si>
+    <t>First Home Super Saver Scheme</t>
+  </si>
+  <si>
     <t>Eligible first home buyers can withdraw voluntary super contributions to help fund their first home deposit.</t>
   </si>
   <si>
-    <t>The First home super saver scheme lets eligible first home buyers withdraw eligible voluntary superannuation contributions to put toward their first home deposit. Eligibility requirements are defined by Australian Taxation Office.</t>
-  </si>
-  <si>
-    <t>https://www.ato.gov.au/individuals-and-families/super-for-individuals-and-families/super/withdrawing-and-using-your-super/early-access-to-super/first-home-super-saver-scheme</t>
+    <t>The First Home Super Saver Scheme lets eligible first home buyers withdraw eligible voluntary superannuation contributions to put toward their first home deposit. Applicants must satisfy ownership and residency requirements defined by Australian Taxation Office.</t>
+  </si>
+  <si>
+    <t>https://firsthomebuyers.gov.au/first-home-super-saver-scheme</t>
   </si>
   <si>
     <t>fed-first-home-super-saver</t>
   </si>
   <si>
-    <t>First home super saver scheme</t>
-  </si>
-  <si>
     <t>FHSSS</t>
   </si>
   <si>
@@ -680,7 +697,7 @@
     <t>Australian Taxation Office</t>
   </si>
   <si>
-    <t>Withdraw voluntary super contributions for a deposit</t>
+    <t>Withdraw up to $50,000 of voluntary super contributions</t>
   </si>
   <si>
     <t>Super withdrawal</t>
@@ -689,7 +706,10 @@
     <t>Withdraw eligible voluntary contributions plus associated earnings</t>
   </si>
   <si>
-    <t>www.ato.gov.au</t>
+    <t>New home; Established home; Vacant land</t>
+  </si>
+  <si>
+    <t>2025-10</t>
   </si>
   <si>
     <t>Super savings</t>
@@ -698,6 +718,9 @@
     <t>Supercharge your deposit through your super.</t>
   </si>
   <si>
+    <t>First Home Buyers Assistance Scheme</t>
+  </si>
+  <si>
     <t>Eligible first home buyers may pay reduced or no stamp duty when buying a home in NSW.</t>
   </si>
   <si>
@@ -710,9 +733,6 @@
     <t>nsw-first-home-buyers-assistance</t>
   </si>
   <si>
-    <t>First Home Buyers Assistance Scheme</t>
-  </si>
-  <si>
     <t>FHBAS</t>
   </si>
   <si>
@@ -761,6 +781,9 @@
     <t>Pay less (or no) stamp duty on your first home.</t>
   </si>
   <si>
+    <t>First home buyer duty exemption or concession</t>
+  </si>
+  <si>
     <t>Eligible first home buyers may pay reduced or no stamp duty when buying a home in VIC.</t>
   </si>
   <si>
@@ -773,9 +796,6 @@
     <t>vic-first-home-buyer-duty-exemption</t>
   </si>
   <si>
-    <t>First home buyer duty exemption or concession</t>
-  </si>
-  <si>
     <t>FBDEC</t>
   </si>
   <si>
@@ -788,12 +808,15 @@
     <t>New home; Established home; Off-the-plan; Vacant land</t>
   </si>
   <si>
-    <t>You are not eligible if you or your spouse or partner have already owned a home or other residential property in Australia.</t>
+    <t>You are not eligible if you, your spouse, or your partner have already owned a home or other residential property in Australia.</t>
   </si>
   <si>
     <t>Full exemption up to $750,000</t>
   </si>
   <si>
+    <t>First home concession</t>
+  </si>
+  <si>
     <t>Eligible first home buyers may pay reduced or no stamp duty when buying a home in QLD.</t>
   </si>
   <si>
@@ -806,9 +829,6 @@
     <t>qld-first-home-transfer-duty-concession</t>
   </si>
   <si>
-    <t>First home concession</t>
-  </si>
-  <si>
     <t>FC</t>
   </si>
   <si>
@@ -833,6 +853,9 @@
     <t>Rooming Accommodation Act 2008</t>
   </si>
   <si>
+    <t>First Home Owner Rate of Duty</t>
+  </si>
+  <si>
     <t>Eligible first home buyers may pay reduced or no stamp duty when buying an established home in WA.</t>
   </si>
   <si>
@@ -845,15 +868,9 @@
     <t>wa-first-home-owner-rate-of-duty</t>
   </si>
   <si>
-    <t>First Home Owner Rate of Duty</t>
-  </si>
-  <si>
     <t>FHOR</t>
   </si>
   <si>
-    <t>Australian citizen</t>
-  </si>
-  <si>
     <t>Varies by location: $800,000, $750,000, $1,000,000</t>
   </si>
   <si>
@@ -884,6 +901,9 @@
     <t>First Home Owner Grant Act 2000; Taxation Administration Act 2003; Duties Act 2008</t>
   </si>
   <si>
+    <t>Home Buyer Concession Scheme</t>
+  </si>
+  <si>
     <t>Eligible first home buyers may pay reduced or no stamp duty when buying a home in ACT.</t>
   </si>
   <si>
@@ -894,9 +914,6 @@
   </si>
   <si>
     <t>act-home-buyer-concession</t>
-  </si>
-  <si>
-    <t>Home Buyer Concession Scheme</t>
   </si>
   <si>
     <t>HBCS</t>
@@ -917,20 +934,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FF111111"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1304,9 +1319,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BI16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1319,10 +1334,10 @@
     <col min="11" max="11" width="31" customWidth="1"/>
     <col min="12" max="13" width="60" customWidth="1"/>
     <col min="14" max="14" width="36" customWidth="1"/>
-    <col min="15" max="15" width="27" customWidth="1"/>
+    <col min="15" max="15" width="47" customWidth="1"/>
     <col min="16" max="16" width="60" customWidth="1"/>
     <col min="17" max="17" width="19" customWidth="1"/>
-    <col min="18" max="18" width="54" customWidth="1"/>
+    <col min="18" max="18" width="57" customWidth="1"/>
     <col min="19" max="19" width="21" customWidth="1"/>
     <col min="20" max="20" width="15" customWidth="1"/>
     <col min="21" max="21" width="33" customWidth="1"/>
@@ -1349,7 +1364,8 @@
     <col min="44" max="44" width="54" customWidth="1"/>
     <col min="45" max="45" width="22" customWidth="1"/>
     <col min="46" max="46" width="25" customWidth="1"/>
-    <col min="47" max="48" width="14" customWidth="1"/>
+    <col min="47" max="47" width="15" customWidth="1"/>
+    <col min="48" max="48" width="14" customWidth="1"/>
     <col min="49" max="49" width="19" customWidth="1"/>
     <col min="50" max="50" width="18" customWidth="1"/>
     <col min="51" max="51" width="36" customWidth="1"/>
@@ -1357,34 +1373,34 @@
     <col min="53" max="54" width="60" customWidth="1"/>
     <col min="55" max="55" width="42" customWidth="1"/>
     <col min="56" max="56" width="20" customWidth="1"/>
-    <col min="57" max="57" width="29" customWidth="1"/>
+    <col min="57" max="57" width="25" customWidth="1"/>
     <col min="58" max="58" width="60" customWidth="1"/>
     <col min="59" max="59" width="22" customWidth="1"/>
     <col min="60" max="60" width="18" customWidth="1"/>
     <col min="61" max="61" width="57" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" ht="30" customHeight="1" spans="1:61" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
@@ -1549,33 +1565,33 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:61" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>68</v>
@@ -1584,10 +1600,10 @@
         <v>69</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>70</v>
@@ -1599,7 +1615,7 @@
         <v>72</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>73</v>
@@ -1707,7 +1723,7 @@
         <v>71</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="BB2" s="2" t="s">
         <v>91</v>
@@ -1734,33 +1750,33 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>67</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>68</v>
@@ -1769,10 +1785,10 @@
         <v>103</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>104</v>
@@ -1784,7 +1800,7 @@
         <v>71</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>73</v>
@@ -1892,7 +1908,7 @@
         <v>107</v>
       </c>
       <c r="BA3" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BB3" s="2" t="s">
         <v>108</v>
@@ -1919,33 +1935,33 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>67</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>68</v>
@@ -1954,10 +1970,10 @@
         <v>116</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>117</v>
@@ -1969,7 +1985,7 @@
         <v>71</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>119</v>
@@ -2077,7 +2093,7 @@
         <v>120</v>
       </c>
       <c r="BA4" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BB4" s="2" t="s">
         <v>71</v>
@@ -2104,15 +2120,15 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>124</v>
@@ -2130,7 +2146,7 @@
         <v>67</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>68</v>
@@ -2154,7 +2170,7 @@
         <v>71</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>73</v>
@@ -2289,15 +2305,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>133</v>
@@ -2315,7 +2331,7 @@
         <v>67</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>68</v>
@@ -2339,7 +2355,7 @@
         <v>71</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>139</v>
@@ -2474,15 +2490,15 @@
         <v>147</v>
       </c>
     </row>
-    <row r="7" spans="1:61" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>148</v>
@@ -2500,7 +2516,7 @@
         <v>67</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>68</v>
@@ -2524,7 +2540,7 @@
         <v>71</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>71</v>
@@ -2659,33 +2675,33 @@
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>162</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>163</v>
@@ -2694,10 +2710,10 @@
         <v>164</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>165</v>
@@ -2709,7 +2725,7 @@
         <v>71</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>73</v>
@@ -2817,7 +2833,7 @@
         <v>71</v>
       </c>
       <c r="BA8" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BB8" s="2" t="s">
         <v>71</v>
@@ -2844,27 +2860,27 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>178</v>
@@ -2879,28 +2895,28 @@
         <v>181</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>182</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>179</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>71</v>
@@ -2912,19 +2928,19 @@
         <v>71</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="X9" s="2" t="s">
         <v>77</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>71</v>
@@ -2936,34 +2952,34 @@
         <v>71</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>186</v>
+        <v>81</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AI9" s="2" t="s">
         <v>130</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>71</v>
+        <v>190</v>
       </c>
       <c r="AK9" s="2" t="s">
         <v>77</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="AM9" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AN9" s="2" t="s">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="AO9" s="2" t="s">
         <v>71</v>
@@ -2990,72 +3006,72 @@
         <v>87</v>
       </c>
       <c r="AW9" s="2" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="AX9" s="2" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="AY9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AZ9" s="2" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
       <c r="BA9" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="BB9" s="2" t="s">
-        <v>71</v>
+        <v>195</v>
       </c>
       <c r="BC9" s="2" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="BD9" s="2" t="s">
         <v>93</v>
       </c>
       <c r="BE9" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="BF9" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="BG9" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="BH9" s="2" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="BI9" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
-    <row r="10" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>180</v>
@@ -3064,10 +3080,10 @@
         <v>181</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>182</v>
@@ -3079,13 +3095,13 @@
         <v>71</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>71</v>
@@ -3097,28 +3113,28 @@
         <v>71</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="X10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y10" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="Y10" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="Z10" s="2" t="s">
-        <v>71</v>
+        <v>210</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>71</v>
+        <v>211</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>71</v>
+        <v>212</v>
       </c>
       <c r="AD10" s="2" t="s">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="AE10" s="2" t="s">
         <v>71</v>
@@ -3127,13 +3143,13 @@
         <v>71</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>130</v>
+        <v>215</v>
       </c>
       <c r="AJ10" s="2" t="s">
         <v>71</v>
@@ -3145,13 +3161,13 @@
         <v>71</v>
       </c>
       <c r="AM10" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AN10" s="2" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="AO10" s="2" t="s">
-        <v>71</v>
+        <v>216</v>
       </c>
       <c r="AP10" s="2" t="s">
         <v>71</v>
@@ -3169,7 +3185,7 @@
         <v>71</v>
       </c>
       <c r="AU10" s="2" t="s">
-        <v>71</v>
+        <v>217</v>
       </c>
       <c r="AV10" s="2" t="s">
         <v>87</v>
@@ -3187,72 +3203,72 @@
         <v>71</v>
       </c>
       <c r="BA10" s="2" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="BB10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="BC10" s="2" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="BD10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="BE10" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="BF10" s="2" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="BG10" s="2" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="BH10" s="2" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="BI10" s="2" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="11" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>180</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>182</v>
@@ -3264,13 +3280,13 @@
         <v>71</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>184</v>
+        <v>229</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>71</v>
@@ -3282,19 +3298,19 @@
         <v>71</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>185</v>
+        <v>230</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>77</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>71</v>
+        <v>210</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>71</v>
@@ -3312,25 +3328,25 @@
         <v>71</v>
       </c>
       <c r="AG11" s="2" t="s">
-        <v>186</v>
+        <v>231</v>
       </c>
       <c r="AH11" s="2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="AL11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AM11" s="2" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="AN11" s="2" t="s">
         <v>71</v>
@@ -3369,93 +3385,93 @@
         <v>71</v>
       </c>
       <c r="AZ11" s="2" t="s">
-        <v>71</v>
+        <v>232</v>
       </c>
       <c r="BA11" s="2" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="BB11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="BC11" s="2" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="BD11" s="2" t="s">
         <v>93</v>
       </c>
       <c r="BE11" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="BF11" s="2" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="BG11" s="2" t="s">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="BH11" s="2" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="BI11" s="2" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="12" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>181</v>
+        <v>69</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>182</v>
+        <v>70</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>71</v>
+        <v>242</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>71</v>
@@ -3467,19 +3483,19 @@
         <v>71</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>77</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>71</v>
@@ -3497,40 +3513,40 @@
         <v>71</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="AK12" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="AL12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AM12" s="2" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="AN12" s="2" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="AO12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AP12" s="2" t="s">
-        <v>71</v>
+        <v>247</v>
       </c>
       <c r="AQ12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AR12" s="2" t="s">
-        <v>71</v>
+        <v>248</v>
       </c>
       <c r="AS12" s="2" t="s">
         <v>71</v>
@@ -3545,87 +3561,87 @@
         <v>87</v>
       </c>
       <c r="AW12" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="AX12" s="2" t="s">
-        <v>71</v>
+        <v>249</v>
       </c>
       <c r="AY12" s="2" t="s">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="AZ12" s="2" t="s">
-        <v>71</v>
+        <v>251</v>
       </c>
       <c r="BA12" s="2" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="BB12" s="2" t="s">
-        <v>71</v>
+        <v>252</v>
       </c>
       <c r="BC12" s="2" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="BD12" s="2" t="s">
         <v>93</v>
       </c>
       <c r="BE12" s="2" t="s">
-        <v>188</v>
+        <v>94</v>
       </c>
       <c r="BF12" s="2" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="BG12" s="2" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="BH12" s="2" t="s">
-        <v>96</v>
+        <v>254</v>
       </c>
       <c r="BI12" s="2" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="13" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>182</v>
+        <v>104</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>71</v>
@@ -3634,13 +3650,13 @@
         <v>71</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>71</v>
@@ -3652,19 +3668,19 @@
         <v>71</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>71</v>
@@ -3676,22 +3692,22 @@
         <v>71</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>71</v>
+        <v>263</v>
       </c>
       <c r="AF13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>71</v>
+        <v>264</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="AI13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="AK13" s="2" t="s">
         <v>71</v>
@@ -3700,22 +3716,22 @@
         <v>71</v>
       </c>
       <c r="AM13" s="2" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="AN13" s="2" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="AO13" s="2" t="s">
-        <v>71</v>
+        <v>265</v>
       </c>
       <c r="AP13" s="2" t="s">
-        <v>71</v>
+        <v>263</v>
       </c>
       <c r="AQ13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AR13" s="2" t="s">
-        <v>71</v>
+        <v>266</v>
       </c>
       <c r="AS13" s="2" t="s">
         <v>71</v>
@@ -3730,102 +3746,102 @@
         <v>87</v>
       </c>
       <c r="AW13" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="AX13" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="AY13" s="2" t="s">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="AZ13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="BA13" s="2" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
       <c r="BB13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="BC13" s="2" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="BD13" s="2" t="s">
         <v>93</v>
       </c>
       <c r="BE13" s="2" t="s">
-        <v>224</v>
+        <v>110</v>
       </c>
       <c r="BF13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="BG13" s="2" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="BH13" s="2" t="s">
-        <v>96</v>
+        <v>254</v>
       </c>
       <c r="BI13" s="2" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="14" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>227</v>
+        <v>268</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>232</v>
+        <v>272</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>68</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>227</v>
+        <v>268</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>234</v>
+        <v>71</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>71</v>
@@ -3837,7 +3853,7 @@
         <v>71</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>77</v>
@@ -3846,7 +3862,7 @@
         <v>77</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="AA14" s="2" t="s">
         <v>79</v>
@@ -3867,7 +3883,7 @@
         <v>71</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="AH14" s="2" t="s">
         <v>82</v>
@@ -3885,22 +3901,22 @@
         <v>71</v>
       </c>
       <c r="AM14" s="2" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="AN14" s="2" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="AO14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AP14" s="2" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="AQ14" s="2" t="s">
-        <v>71</v>
+        <v>275</v>
       </c>
       <c r="AR14" s="2" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="AS14" s="2" t="s">
         <v>71</v>
@@ -3915,87 +3931,87 @@
         <v>87</v>
       </c>
       <c r="AW14" s="2" t="s">
-        <v>89</v>
+        <v>277</v>
       </c>
       <c r="AX14" s="2" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="AY14" s="2" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="AZ14" s="2" t="s">
-        <v>243</v>
+        <v>71</v>
       </c>
       <c r="BA14" s="2" t="s">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="BB14" s="2" t="s">
-        <v>244</v>
+        <v>279</v>
       </c>
       <c r="BC14" s="2" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="BD14" s="2" t="s">
         <v>93</v>
       </c>
       <c r="BE14" s="2" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="BF14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="BG14" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="BH14" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="BI14" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="15" spans="1:61" s="2" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>251</v>
+        <v>284</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>249</v>
+        <v>282</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>71</v>
@@ -4004,13 +4020,13 @@
         <v>71</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="T15" s="2" t="s">
         <v>71</v>
@@ -4022,19 +4038,19 @@
         <v>71</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="X15" s="2" t="s">
         <v>77</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>71</v>
@@ -4046,22 +4062,22 @@
         <v>71</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>71</v>
+        <v>286</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="AI15" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="AK15" s="2" t="s">
         <v>71</v>
@@ -4073,19 +4089,19 @@
         <v>141</v>
       </c>
       <c r="AN15" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="AO15" s="2" t="s">
-        <v>257</v>
+        <v>71</v>
       </c>
       <c r="AP15" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="AQ15" s="2" t="s">
-        <v>71</v>
+        <v>289</v>
       </c>
       <c r="AR15" s="2" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="AS15" s="2" t="s">
         <v>71</v>
@@ -4100,22 +4116,22 @@
         <v>87</v>
       </c>
       <c r="AW15" s="2" t="s">
-        <v>89</v>
+        <v>291</v>
       </c>
       <c r="AX15" s="2" t="s">
-        <v>89</v>
+        <v>292</v>
       </c>
       <c r="AY15" s="2" t="s">
-        <v>242</v>
+        <v>293</v>
       </c>
       <c r="AZ15" s="2" t="s">
-        <v>71</v>
+        <v>294</v>
       </c>
       <c r="BA15" s="2" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="BB15" s="2" t="s">
-        <v>71</v>
+        <v>295</v>
       </c>
       <c r="BC15" s="2" t="s">
         <v>121</v>
@@ -4124,63 +4140,63 @@
         <v>93</v>
       </c>
       <c r="BE15" s="2" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="BF15" s="2" t="s">
         <v>71</v>
       </c>
       <c r="BG15" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="BH15" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="BI15" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="16" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:61" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>260</v>
+        <v>298</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>116</v>
+        <v>302</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>260</v>
+        <v>298</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>117</v>
+        <v>303</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>71</v>
@@ -4189,13 +4205,13 @@
         <v>71</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>71</v>
@@ -4207,19 +4223,19 @@
         <v>71</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="X16" s="2" t="s">
         <v>77</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="Z16" s="2" t="s">
-        <v>166</v>
+        <v>71</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>71</v>
@@ -4237,16 +4253,16 @@
         <v>71</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>265</v>
+        <v>71</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="AI16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AJ16" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="AK16" s="2" t="s">
         <v>71</v>
@@ -4255,22 +4271,22 @@
         <v>71</v>
       </c>
       <c r="AM16" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="AN16" s="2" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="AO16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="AP16" s="2" t="s">
-        <v>266</v>
+        <v>71</v>
       </c>
       <c r="AQ16" s="2" t="s">
-        <v>267</v>
+        <v>71</v>
       </c>
       <c r="AR16" s="2" t="s">
-        <v>268</v>
+        <v>71</v>
       </c>
       <c r="AS16" s="2" t="s">
         <v>71</v>
@@ -4285,417 +4301,47 @@
         <v>87</v>
       </c>
       <c r="AW16" s="2" t="s">
-        <v>269</v>
+        <v>71</v>
       </c>
       <c r="AX16" s="2" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="AY16" s="2" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="AZ16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="BA16" s="2" t="s">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="BB16" s="2" t="s">
-        <v>271</v>
+        <v>71</v>
       </c>
       <c r="BC16" s="2" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="BD16" s="2" t="s">
         <v>93</v>
       </c>
       <c r="BE16" s="2" t="s">
-        <v>122</v>
+        <v>305</v>
       </c>
       <c r="BF16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="BG16" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="BH16" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="BI16" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="17" spans="1:61" s="2" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z17" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE17" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="AF17" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AG17" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AH17" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AI17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AK17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AM17" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AN17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP17" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="AQ17" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AR17" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="AS17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AT17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AU17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AV17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW17" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="AX17" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="AY17" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="AZ17" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="BA17" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="BB17" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="BC17" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="BD17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="BE17" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BF17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="BG17" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="BH17" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="BI17" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="18" spans="1:61" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AJ18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AK18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AM18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AN18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AP18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AR18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AS18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AT18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AU18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AV18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AX18" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="AY18" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="AZ18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="BA18" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="BB18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="BC18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="BD18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="BE18" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="BF18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="BG18" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="BH18" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="BI18" s="2" t="s">
-        <v>247</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/government-data-extractor/output/government_schemes.xlsx
+++ b/government-data-extractor/output/government_schemes.xlsx
@@ -193,7 +193,7 @@
     <t>Priority/Ranking</t>
   </si>
   <si>
-    <t>Catchy Line/Hook</t>
+    <t>UI/UX Reference</t>
   </si>
   <si>
     <t>Grant</t>
@@ -4342,6 +4342,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>